--- a/manuscript/submission_data/source_data/Source_Data_Supplementary_Figure_13.xlsx
+++ b/manuscript/submission_data/source_data/Source_Data_Supplementary_Figure_13.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Panel_A" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Panel_B" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Panel_C" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Panel_A" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Panel_B" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Panel_C" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -23943,7 +23943,7 @@
     <row r="313">
       <c r="A313" t="inlineStr">
         <is>
-          <t>manuscript/supplementary/Supplementary_Table_7_Cohort_Flow_and_Tree_Selection.tsv</t>
+          <t>manuscript/supplementary/Supplementary_Table_4_Cohort_Flow_and_Tree_Selection.tsv</t>
         </is>
       </c>
       <c r="B313" t="inlineStr">
@@ -24006,7 +24006,11 @@
           <t>3370</t>
         </is>
       </c>
-      <c r="D316" t="inlineStr"/>
+      <c r="D316" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
       <c r="E316" t="inlineStr">
         <is>
           <t>pertussis_data/pertussis_gene/step1_ingest/outputs/bp_public_genome_manifest.tsv</t>
@@ -24051,7 +24055,7 @@
       </c>
       <c r="F317" t="inlineStr">
         <is>
-          <t>Combined manuscript manifest after public-assembly QC, read-rescue provenance assignment, and de novo public-read augmentation.</t>
+          <t>Current combined manifest after public-assembly QC, read-rescue provenance assignment, and de novo public-read augmentation.</t>
         </is>
       </c>
       <c r="G317" t="inlineStr">
@@ -24083,17 +24087,17 @@
       </c>
       <c r="E318" t="inlineStr">
         <is>
-          <t>pertussis_data/pertussis_gene/step4_prn_validation/outputs/bp_prn_mechanism_calls.tsv</t>
+          <t>manuscript/figure_data/fig05_evidence_chain_summary.tsv</t>
         </is>
       </c>
       <c r="F318" t="inlineStr">
         <is>
-          <t>Mechanism call in {intact, coding_disrupted_is481, coding_disrupted_inversion_or_rearrangement, coding_disrupted_other}.</t>
+          <t>Frozen manuscript-facing event/phenotype frame: intact-locus boundary calls plus structurally resolved disrupted event-class calls.</t>
         </is>
       </c>
       <c r="G318" t="inlineStr">
         <is>
-          <t>Mechanism-call table interpretable subset used for broad mechanism summaries.</t>
+          <t>Frozen frame comprises 748 intact-locus boundary calls and 577 structurally resolved disrupted event-class calls.</t>
         </is>
       </c>
     </row>
@@ -24113,20 +24117,24 @@
           <t>1081</t>
         </is>
       </c>
-      <c r="D319" t="inlineStr"/>
+      <c r="D319" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
       <c r="E319" t="inlineStr">
         <is>
-          <t>pertussis_data/pertussis_gene/step4_prn_validation/outputs/bp_prn_mechanism_calls.tsv</t>
+          <t>manuscript/figure_data/fig05_evidence_chain_summary.tsv</t>
         </is>
       </c>
       <c r="F319" t="inlineStr">
         <is>
-          <t>Mechanism call in {insufficient_data, uncertain_fragmented_assembly}.</t>
+          <t>Retained records outside the frozen manuscript-facing event/phenotype frame.</t>
         </is>
       </c>
       <c r="G319" t="inlineStr">
         <is>
-          <t>1052 insufficient plus 29 uncertain fragmented assemblies.</t>
+          <t>Frozen non-interpretable or uncertain records enter missingness bounds rather than event-concentration denominators.</t>
         </is>
       </c>
     </row>
@@ -24146,7 +24154,11 @@
           <t>1579</t>
         </is>
       </c>
-      <c r="D320" t="inlineStr"/>
+      <c r="D320" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
       <c r="E320" t="inlineStr">
         <is>
           <t>pertussis_data/pertussis_gene/step1_ingest/outputs/bp_public_genome_qc_manifest.tsv</t>
@@ -24179,7 +24191,11 @@
           <t>66</t>
         </is>
       </c>
-      <c r="D321" t="inlineStr"/>
+      <c r="D321" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
       <c r="E321" t="inlineStr">
         <is>
           <t>pertussis_data/pertussis_gene/step4_prn_validation/outputs/bp_prn_read_validation.tsv</t>
@@ -24212,7 +24228,11 @@
           <t>1951</t>
         </is>
       </c>
-      <c r="D322" t="inlineStr"/>
+      <c r="D322" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
       <c r="E322" t="inlineStr">
         <is>
           <t>outputs/workflow/snippy_ctg/snippy_ctg_plan.tsv</t>
@@ -24220,12 +24240,12 @@
       </c>
       <c r="F322" t="inlineStr">
         <is>
-          <t>include_in_snippy_ctg == True in the Snippy contig-mode plan.</t>
+          <t>include_in_snippy_ctg == True in the current Snippy contig-mode plan.</t>
         </is>
       </c>
       <c r="G322" t="inlineStr">
         <is>
-          <t>This is an operational ML-tree eligibility layer used for tree construction, not a primary representativeness claim.</t>
+          <t>This is an operational ML-tree eligibility layer, not yet a manuscript-facing representativeness contract.</t>
         </is>
       </c>
     </row>
@@ -24245,7 +24265,11 @@
           <t>1952</t>
         </is>
       </c>
-      <c r="D323" t="inlineStr"/>
+      <c r="D323" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
       <c r="E323" t="inlineStr">
         <is>
           <t>outputs/workflow/phylo/core.full.aln</t>
@@ -24278,7 +24302,11 @@
           <t>0</t>
         </is>
       </c>
-      <c r="D324" t="inlineStr"/>
+      <c r="D324" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
       <c r="E324" t="inlineStr">
         <is>
           <t>outputs/workflow/phylo/pre_gubbins_missingness.tsv</t>
@@ -24291,7 +24319,7 @@
       </c>
       <c r="G324" t="inlineStr">
         <is>
-          <t>The analysis excludes only GCA_000212975.1 at missing_fraction=0.889548.</t>
+          <t>Current rerun excludes only GCA_000212975.1 at missing_fraction=0.889548.</t>
         </is>
       </c>
     </row>
@@ -24311,7 +24339,11 @@
           <t>1952</t>
         </is>
       </c>
-      <c r="D325" t="inlineStr"/>
+      <c r="D325" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
       <c r="E325" t="inlineStr">
         <is>
           <t>outputs/workflow/asr/tip_states.tsv</t>
@@ -24344,7 +24376,11 @@
           <t>1951</t>
         </is>
       </c>
-      <c r="D326" t="inlineStr"/>
+      <c r="D326" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
       <c r="E326" t="inlineStr">
         <is>
           <t>outputs/workflow/asr/tip_states.tsv</t>
@@ -24357,7 +24393,7 @@
       </c>
       <c r="G326" t="inlineStr">
         <is>
-          <t>Non-reference state counts: intact=617, disrupted=573, insufficient_data=761.</t>
+          <t>Non-reference state counts: intact=1229, disrupted=561, insufficient_data=161.</t>
         </is>
       </c>
     </row>
@@ -24377,7 +24413,11 @@
           <t>1919</t>
         </is>
       </c>
-      <c r="D327" t="inlineStr"/>
+      <c r="D327" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
       <c r="E327" t="inlineStr">
         <is>
           <t>outputs/workflow/asr_sensitivity/composition_filtered/tip_states.tsv</t>
@@ -24410,7 +24450,11 @@
           <t>1918</t>
         </is>
       </c>
-      <c r="D328" t="inlineStr"/>
+      <c r="D328" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
       <c r="E328" t="inlineStr">
         <is>
           <t>outputs/workflow/asr_sensitivity/composition_filtered/tip_states.tsv</t>
@@ -24423,7 +24467,7 @@
       </c>
       <c r="G328" t="inlineStr">
         <is>
-          <t>Non-reference state counts: intact=612, disrupted=571, insufficient_data=735.</t>
+          <t>Non-reference state counts: intact=1202, disrupted=559, insufficient_data=157.</t>
         </is>
       </c>
     </row>
@@ -47954,7 +47998,7 @@
     <row r="313">
       <c r="A313" t="inlineStr">
         <is>
-          <t>manuscript/supplementary/Supplementary_Table_7_Cohort_Flow_and_Tree_Selection.tsv</t>
+          <t>manuscript/supplementary/Supplementary_Table_4_Cohort_Flow_and_Tree_Selection.tsv</t>
         </is>
       </c>
       <c r="B313" t="inlineStr">
@@ -48017,7 +48061,11 @@
           <t>3370</t>
         </is>
       </c>
-      <c r="D316" t="inlineStr"/>
+      <c r="D316" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
       <c r="E316" t="inlineStr">
         <is>
           <t>pertussis_data/pertussis_gene/step1_ingest/outputs/bp_public_genome_manifest.tsv</t>
@@ -48062,7 +48110,7 @@
       </c>
       <c r="F317" t="inlineStr">
         <is>
-          <t>Combined manuscript manifest after public-assembly QC, read-rescue provenance assignment, and de novo public-read augmentation.</t>
+          <t>Current combined manifest after public-assembly QC, read-rescue provenance assignment, and de novo public-read augmentation.</t>
         </is>
       </c>
       <c r="G317" t="inlineStr">
@@ -48094,17 +48142,17 @@
       </c>
       <c r="E318" t="inlineStr">
         <is>
-          <t>pertussis_data/pertussis_gene/step4_prn_validation/outputs/bp_prn_mechanism_calls.tsv</t>
+          <t>manuscript/figure_data/fig05_evidence_chain_summary.tsv</t>
         </is>
       </c>
       <c r="F318" t="inlineStr">
         <is>
-          <t>Mechanism call in {intact, coding_disrupted_is481, coding_disrupted_inversion_or_rearrangement, coding_disrupted_other}.</t>
+          <t>Frozen manuscript-facing event/phenotype frame: intact-locus boundary calls plus structurally resolved disrupted event-class calls.</t>
         </is>
       </c>
       <c r="G318" t="inlineStr">
         <is>
-          <t>Mechanism-call table interpretable subset used for broad mechanism summaries.</t>
+          <t>Frozen frame comprises 748 intact-locus boundary calls and 577 structurally resolved disrupted event-class calls.</t>
         </is>
       </c>
     </row>
@@ -48124,20 +48172,24 @@
           <t>1081</t>
         </is>
       </c>
-      <c r="D319" t="inlineStr"/>
+      <c r="D319" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
       <c r="E319" t="inlineStr">
         <is>
-          <t>pertussis_data/pertussis_gene/step4_prn_validation/outputs/bp_prn_mechanism_calls.tsv</t>
+          <t>manuscript/figure_data/fig05_evidence_chain_summary.tsv</t>
         </is>
       </c>
       <c r="F319" t="inlineStr">
         <is>
-          <t>Mechanism call in {insufficient_data, uncertain_fragmented_assembly}.</t>
+          <t>Retained records outside the frozen manuscript-facing event/phenotype frame.</t>
         </is>
       </c>
       <c r="G319" t="inlineStr">
         <is>
-          <t>1052 insufficient plus 29 uncertain fragmented assemblies.</t>
+          <t>Frozen non-interpretable or uncertain records enter missingness bounds rather than event-concentration denominators.</t>
         </is>
       </c>
     </row>
@@ -48157,7 +48209,11 @@
           <t>1579</t>
         </is>
       </c>
-      <c r="D320" t="inlineStr"/>
+      <c r="D320" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
       <c r="E320" t="inlineStr">
         <is>
           <t>pertussis_data/pertussis_gene/step1_ingest/outputs/bp_public_genome_qc_manifest.tsv</t>
@@ -48190,7 +48246,11 @@
           <t>66</t>
         </is>
       </c>
-      <c r="D321" t="inlineStr"/>
+      <c r="D321" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
       <c r="E321" t="inlineStr">
         <is>
           <t>pertussis_data/pertussis_gene/step4_prn_validation/outputs/bp_prn_read_validation.tsv</t>
@@ -48223,7 +48283,11 @@
           <t>1951</t>
         </is>
       </c>
-      <c r="D322" t="inlineStr"/>
+      <c r="D322" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
       <c r="E322" t="inlineStr">
         <is>
           <t>outputs/workflow/snippy_ctg/snippy_ctg_plan.tsv</t>
@@ -48231,12 +48295,12 @@
       </c>
       <c r="F322" t="inlineStr">
         <is>
-          <t>include_in_snippy_ctg == True in the Snippy contig-mode plan.</t>
+          <t>include_in_snippy_ctg == True in the current Snippy contig-mode plan.</t>
         </is>
       </c>
       <c r="G322" t="inlineStr">
         <is>
-          <t>This is an operational ML-tree eligibility layer used for tree construction, not a primary representativeness claim.</t>
+          <t>This is an operational ML-tree eligibility layer, not yet a manuscript-facing representativeness contract.</t>
         </is>
       </c>
     </row>
@@ -48256,7 +48320,11 @@
           <t>1952</t>
         </is>
       </c>
-      <c r="D323" t="inlineStr"/>
+      <c r="D323" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
       <c r="E323" t="inlineStr">
         <is>
           <t>outputs/workflow/phylo/core.full.aln</t>
@@ -48289,7 +48357,11 @@
           <t>0</t>
         </is>
       </c>
-      <c r="D324" t="inlineStr"/>
+      <c r="D324" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
       <c r="E324" t="inlineStr">
         <is>
           <t>outputs/workflow/phylo/pre_gubbins_missingness.tsv</t>
@@ -48302,7 +48374,7 @@
       </c>
       <c r="G324" t="inlineStr">
         <is>
-          <t>The analysis excludes only GCA_000212975.1 at missing_fraction=0.889548.</t>
+          <t>Current rerun excludes only GCA_000212975.1 at missing_fraction=0.889548.</t>
         </is>
       </c>
     </row>
@@ -48322,7 +48394,11 @@
           <t>1952</t>
         </is>
       </c>
-      <c r="D325" t="inlineStr"/>
+      <c r="D325" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
       <c r="E325" t="inlineStr">
         <is>
           <t>outputs/workflow/asr/tip_states.tsv</t>
@@ -48355,7 +48431,11 @@
           <t>1951</t>
         </is>
       </c>
-      <c r="D326" t="inlineStr"/>
+      <c r="D326" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
       <c r="E326" t="inlineStr">
         <is>
           <t>outputs/workflow/asr/tip_states.tsv</t>
@@ -48368,7 +48448,7 @@
       </c>
       <c r="G326" t="inlineStr">
         <is>
-          <t>Non-reference state counts: intact=617, disrupted=573, insufficient_data=761.</t>
+          <t>Non-reference state counts: intact=1229, disrupted=561, insufficient_data=161.</t>
         </is>
       </c>
     </row>
@@ -48388,7 +48468,11 @@
           <t>1919</t>
         </is>
       </c>
-      <c r="D327" t="inlineStr"/>
+      <c r="D327" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
       <c r="E327" t="inlineStr">
         <is>
           <t>outputs/workflow/asr_sensitivity/composition_filtered/tip_states.tsv</t>
@@ -48421,7 +48505,11 @@
           <t>1918</t>
         </is>
       </c>
-      <c r="D328" t="inlineStr"/>
+      <c r="D328" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
       <c r="E328" t="inlineStr">
         <is>
           <t>outputs/workflow/asr_sensitivity/composition_filtered/tip_states.tsv</t>
@@ -48434,7 +48522,7 @@
       </c>
       <c r="G328" t="inlineStr">
         <is>
-          <t>Non-reference state counts: intact=612, disrupted=571, insufficient_data=735.</t>
+          <t>Non-reference state counts: intact=1202, disrupted=559, insufficient_data=157.</t>
         </is>
       </c>
     </row>
@@ -71965,7 +72053,7 @@
     <row r="313">
       <c r="A313" t="inlineStr">
         <is>
-          <t>manuscript/supplementary/Supplementary_Table_7_Cohort_Flow_and_Tree_Selection.tsv</t>
+          <t>manuscript/supplementary/Supplementary_Table_4_Cohort_Flow_and_Tree_Selection.tsv</t>
         </is>
       </c>
       <c r="B313" t="inlineStr">
@@ -72028,7 +72116,11 @@
           <t>3370</t>
         </is>
       </c>
-      <c r="D316" t="inlineStr"/>
+      <c r="D316" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
       <c r="E316" t="inlineStr">
         <is>
           <t>pertussis_data/pertussis_gene/step1_ingest/outputs/bp_public_genome_manifest.tsv</t>
@@ -72073,7 +72165,7 @@
       </c>
       <c r="F317" t="inlineStr">
         <is>
-          <t>Combined manuscript manifest after public-assembly QC, read-rescue provenance assignment, and de novo public-read augmentation.</t>
+          <t>Current combined manifest after public-assembly QC, read-rescue provenance assignment, and de novo public-read augmentation.</t>
         </is>
       </c>
       <c r="G317" t="inlineStr">
@@ -72105,17 +72197,17 @@
       </c>
       <c r="E318" t="inlineStr">
         <is>
-          <t>pertussis_data/pertussis_gene/step4_prn_validation/outputs/bp_prn_mechanism_calls.tsv</t>
+          <t>manuscript/figure_data/fig05_evidence_chain_summary.tsv</t>
         </is>
       </c>
       <c r="F318" t="inlineStr">
         <is>
-          <t>Mechanism call in {intact, coding_disrupted_is481, coding_disrupted_inversion_or_rearrangement, coding_disrupted_other}.</t>
+          <t>Frozen manuscript-facing event/phenotype frame: intact-locus boundary calls plus structurally resolved disrupted event-class calls.</t>
         </is>
       </c>
       <c r="G318" t="inlineStr">
         <is>
-          <t>Mechanism-call table interpretable subset used for broad mechanism summaries.</t>
+          <t>Frozen frame comprises 748 intact-locus boundary calls and 577 structurally resolved disrupted event-class calls.</t>
         </is>
       </c>
     </row>
@@ -72135,20 +72227,24 @@
           <t>1081</t>
         </is>
       </c>
-      <c r="D319" t="inlineStr"/>
+      <c r="D319" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
       <c r="E319" t="inlineStr">
         <is>
-          <t>pertussis_data/pertussis_gene/step4_prn_validation/outputs/bp_prn_mechanism_calls.tsv</t>
+          <t>manuscript/figure_data/fig05_evidence_chain_summary.tsv</t>
         </is>
       </c>
       <c r="F319" t="inlineStr">
         <is>
-          <t>Mechanism call in {insufficient_data, uncertain_fragmented_assembly}.</t>
+          <t>Retained records outside the frozen manuscript-facing event/phenotype frame.</t>
         </is>
       </c>
       <c r="G319" t="inlineStr">
         <is>
-          <t>1052 insufficient plus 29 uncertain fragmented assemblies.</t>
+          <t>Frozen non-interpretable or uncertain records enter missingness bounds rather than event-concentration denominators.</t>
         </is>
       </c>
     </row>
@@ -72168,7 +72264,11 @@
           <t>1579</t>
         </is>
       </c>
-      <c r="D320" t="inlineStr"/>
+      <c r="D320" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
       <c r="E320" t="inlineStr">
         <is>
           <t>pertussis_data/pertussis_gene/step1_ingest/outputs/bp_public_genome_qc_manifest.tsv</t>
@@ -72201,7 +72301,11 @@
           <t>66</t>
         </is>
       </c>
-      <c r="D321" t="inlineStr"/>
+      <c r="D321" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
       <c r="E321" t="inlineStr">
         <is>
           <t>pertussis_data/pertussis_gene/step4_prn_validation/outputs/bp_prn_read_validation.tsv</t>
@@ -72234,7 +72338,11 @@
           <t>1951</t>
         </is>
       </c>
-      <c r="D322" t="inlineStr"/>
+      <c r="D322" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
       <c r="E322" t="inlineStr">
         <is>
           <t>outputs/workflow/snippy_ctg/snippy_ctg_plan.tsv</t>
@@ -72242,12 +72350,12 @@
       </c>
       <c r="F322" t="inlineStr">
         <is>
-          <t>include_in_snippy_ctg == True in the Snippy contig-mode plan.</t>
+          <t>include_in_snippy_ctg == True in the current Snippy contig-mode plan.</t>
         </is>
       </c>
       <c r="G322" t="inlineStr">
         <is>
-          <t>This is an operational ML-tree eligibility layer used for tree construction, not a primary representativeness claim.</t>
+          <t>This is an operational ML-tree eligibility layer, not yet a manuscript-facing representativeness contract.</t>
         </is>
       </c>
     </row>
@@ -72267,7 +72375,11 @@
           <t>1952</t>
         </is>
       </c>
-      <c r="D323" t="inlineStr"/>
+      <c r="D323" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
       <c r="E323" t="inlineStr">
         <is>
           <t>outputs/workflow/phylo/core.full.aln</t>
@@ -72300,7 +72412,11 @@
           <t>0</t>
         </is>
       </c>
-      <c r="D324" t="inlineStr"/>
+      <c r="D324" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
       <c r="E324" t="inlineStr">
         <is>
           <t>outputs/workflow/phylo/pre_gubbins_missingness.tsv</t>
@@ -72313,7 +72429,7 @@
       </c>
       <c r="G324" t="inlineStr">
         <is>
-          <t>The analysis excludes only GCA_000212975.1 at missing_fraction=0.889548.</t>
+          <t>Current rerun excludes only GCA_000212975.1 at missing_fraction=0.889548.</t>
         </is>
       </c>
     </row>
@@ -72333,7 +72449,11 @@
           <t>1952</t>
         </is>
       </c>
-      <c r="D325" t="inlineStr"/>
+      <c r="D325" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
       <c r="E325" t="inlineStr">
         <is>
           <t>outputs/workflow/asr/tip_states.tsv</t>
@@ -72366,7 +72486,11 @@
           <t>1951</t>
         </is>
       </c>
-      <c r="D326" t="inlineStr"/>
+      <c r="D326" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
       <c r="E326" t="inlineStr">
         <is>
           <t>outputs/workflow/asr/tip_states.tsv</t>
@@ -72379,7 +72503,7 @@
       </c>
       <c r="G326" t="inlineStr">
         <is>
-          <t>Non-reference state counts: intact=617, disrupted=573, insufficient_data=761.</t>
+          <t>Non-reference state counts: intact=1229, disrupted=561, insufficient_data=161.</t>
         </is>
       </c>
     </row>
@@ -72399,7 +72523,11 @@
           <t>1919</t>
         </is>
       </c>
-      <c r="D327" t="inlineStr"/>
+      <c r="D327" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
       <c r="E327" t="inlineStr">
         <is>
           <t>outputs/workflow/asr_sensitivity/composition_filtered/tip_states.tsv</t>
@@ -72432,7 +72560,11 @@
           <t>1918</t>
         </is>
       </c>
-      <c r="D328" t="inlineStr"/>
+      <c r="D328" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
       <c r="E328" t="inlineStr">
         <is>
           <t>outputs/workflow/asr_sensitivity/composition_filtered/tip_states.tsv</t>
@@ -72445,7 +72577,7 @@
       </c>
       <c r="G328" t="inlineStr">
         <is>
-          <t>Non-reference state counts: intact=612, disrupted=571, insufficient_data=735.</t>
+          <t>Non-reference state counts: intact=1202, disrupted=559, insufficient_data=157.</t>
         </is>
       </c>
     </row>
